--- a/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,81</t>
+          <t>0,0; 15,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,63</t>
+          <t>0,0; 16,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,92</t>
+          <t>0,0; 15,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 11,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 0,0</t>
+          <t>-18,03; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 0,0</t>
+          <t>-18,05; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,0</t>
+          <t>-8,13; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 0,0</t>
+          <t>-9,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 0,0</t>
+          <t>-24,62; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 0,0</t>
+          <t>-30,31; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 0,0</t>
+          <t>-10,02; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 0,0</t>
+          <t>-8,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 1,11</t>
+          <t>-10,51; 1,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 0,0</t>
+          <t>-11,43; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 1,89</t>
+          <t>-8,19; 1,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,77</t>
+          <t>-6,11; 2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,03</t>
+          <t>-6,51; 1,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,38</t>
+          <t>-7,08; 0,23</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 2,29</t>
+          <t>-15,08; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,33</t>
+          <t>-14,48; 2,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 1,98</t>
+          <t>-7,71; 2,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,0</t>
+          <t>-6,62; 3,9</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,68</t>
+          <t>0,0; 22,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,16</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,14</t>
+          <t>-3,18; 2,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,79</t>
+          <t>-4,29; 0,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,65</t>
+          <t>-3,13; 1,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,6</t>
+          <t>-3,31; 1,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,21</t>
+          <t>-2,1; 1,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,46</t>
+          <t>-2,88; 0,55</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,67; 337,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 404,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,63; 169,31</t>
+          <t>-72,84; 160,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-89,51; 81,06</t>
+          <t>-90,09; 77,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,31</t>
+          <t>0,0; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,9</t>
+          <t>0,0; 14,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,9</t>
+          <t>0,0; 13,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,04</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 0,0</t>
+          <t>-18,25; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 0,0</t>
+          <t>-17,24; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 0,0</t>
+          <t>-7,03; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,0</t>
+          <t>-8,66; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 0,0</t>
+          <t>-30,04; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 0,0</t>
+          <t>-29,51; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,0</t>
+          <t>-10,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 1,15</t>
+          <t>-11,24; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 0,0</t>
+          <t>-11,67; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,84</t>
+          <t>-7,46; 1,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,79</t>
+          <t>-7,37; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 1,01</t>
+          <t>-6,11; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,23</t>
+          <t>-6,92; 0,21</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 1,81</t>
+          <t>-16,44; 1,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 2,46</t>
+          <t>-14,35; 2,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 2,7</t>
+          <t>-8,0; 2,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,9</t>
+          <t>-6,62; 3,71</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,68</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,15</t>
+          <t>0,0; 19,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,76</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,07</t>
+          <t>-3,33; 2,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,73</t>
+          <t>-4,32; 0,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,54</t>
+          <t>-3,12; 1,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,65</t>
+          <t>-3,09; 1,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,3</t>
+          <t>-2,05; 1,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,55</t>
+          <t>-2,75; 0,52</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,16; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,36; 260,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 404,48</t>
+          <t>-100,0; 330,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 160,32</t>
+          <t>-71,88; 171,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 77,18</t>
+          <t>-88,81; 86,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Clase-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2,98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,08</t>
+          <t>0,0; 14,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,32</t>
+          <t>0,0; 14,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,28; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,85; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,0</t>
+          <t>-7,72; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 0,0</t>
+          <t>-8,67; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-5,88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-5,88</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-27,71; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-29,68; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,0</t>
+          <t>-8,83; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 0,0</t>
+          <t>-8,13; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,69</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,13</t>
+          <t>-7,8; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 0,0</t>
+          <t>-7,45; 2,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,9</t>
+          <t>-10,18; 1,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,75</t>
+          <t>-11,41; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,03</t>
+          <t>-5,85; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,21</t>
+          <t>-6,9; 0,38</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-49,19%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-26,88%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-69,72%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-49,19%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-26,88%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>3,19</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,34</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>-15,86; 2,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>-16,6; 3,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 1,82</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 2,09</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 2,65</t>
+          <t>-8,14; 1,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,71</t>
+          <t>-6,56; 4,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-66,65%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-61,77%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-66,65%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-61,77%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,47</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>6,94</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,49</t>
+          <t>0,0; 18,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,46</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 18,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,21</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-1,13</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,14</t>
+          <t>-3,22; 1,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,73</t>
+          <t>-3,54; 1,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,59</t>
+          <t>-3,41; 2,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,34</t>
+          <t>-4,13; 0,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,3</t>
+          <t>-2,34; 1,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,52</t>
+          <t>-3,14; 0,46</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-24,21%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-32,66%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-11,18%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-60,8%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-24,21%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-32,66%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-91,16; —</t>
+          <t>-95,67; 337,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 260,53</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 171,78</t>
+          <t>-78,63; 169,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 86,7</t>
+          <t>-89,51; 81,06</t>
         </is>
       </c>
     </row>
